--- a/Output/MACD Normal Divergences_19 Jul 2026.xlsx
+++ b/Output/MACD Normal Divergences_19 Jul 2026.xlsx
@@ -7,11 +7,9 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="15 Min" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Hourly" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Daily" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Weekly" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Monthly" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Daily" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Weekly" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Monthly" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -21,13 +19,16 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="1">
+  <fonts count="2">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -38,7 +39,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -46,12 +47,21 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -417,66 +427,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L37"/>
+  <dimension ref="A1:L47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Trend</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Setup</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Divergence</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Zone</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Confluence</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Bias</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>TV_Link</t>
         </is>
@@ -485,7 +495,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>PATANJALI</t>
+          <t>SRF</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -498,7 +508,7 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bullish ND</t>
+          <t>Bearish ND</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -508,14 +518,14 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APATANJALI</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASRF</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>SUZLON</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -538,14 +548,14 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASUZLON</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AIEX</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>BIOCON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -558,7 +568,7 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bullish ND</t>
+          <t>Bearish ND</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -568,14 +578,14 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AJSWSTEEL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABIOCON</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>INOXWIND</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -588,7 +598,7 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bearish ND</t>
+          <t>Bullish ND</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -598,14 +608,14 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AM&amp;M</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AINOXWIND</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>INDUSINDBK</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -628,14 +638,14 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AINDUSINDBK</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIENSOL</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>SWIGGY</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -658,14 +668,14 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASWIGGY</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ALAURUSLABS</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>SWIGGY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -678,7 +688,7 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bearish ND</t>
+          <t>Bullish ND</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -688,14 +698,14 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AEICHERMOT</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASWIGGY</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -718,14 +728,14 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATRENT</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AEICHERMOT</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>ICICIGI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -738,7 +748,7 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bearish ND</t>
+          <t>Bullish ND</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -748,14 +758,14 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ARELIANCE</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AICICIGI</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>KEI</t>
+          <t>SOLARINDS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -768,7 +778,7 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bullish ND</t>
+          <t>Bearish ND</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -778,7 +788,7 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AKEI</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASOLARINDS</t>
         </is>
       </c>
     </row>
@@ -798,7 +808,7 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bullish ND</t>
+          <t>Bearish ND</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -815,7 +825,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>HAVELLS</t>
+          <t>PIIND</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -838,14 +848,14 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHAVELLS</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APIIND</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -858,7 +868,7 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bullish ND</t>
+          <t>Bearish ND</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -868,14 +878,14 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APOLYCAB</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMPHASIS</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>BAJAJ_AUTO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -898,14 +908,14 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMOTHERSON</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABAJAJ_AUTO</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>MOTILALOFS</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -918,7 +928,7 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bullish ND</t>
+          <t>Bearish ND</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -928,14 +938,14 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AJINDALSTEL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMOTILALOFS</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BDL</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -948,7 +958,7 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bullish ND</t>
+          <t>Bearish ND</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -958,14 +968,14 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABDL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACOFORGE</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>JIOFIN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -978,7 +988,7 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bullish ND</t>
+          <t>Bearish ND</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -988,14 +998,14 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAUBANK</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AJIOFIN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>TATAELXSI</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1018,14 +1028,14 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATATAELXSI</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMCX</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BLUESTARCO</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1038,7 +1048,7 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bullish ND</t>
+          <t>Bearish ND</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -1048,14 +1058,14 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABLUESTARCO</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACGPOWER</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>PHOENIXLTD</t>
+          <t>GRASIM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1068,7 +1078,7 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bullish ND</t>
+          <t>Bearish ND</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -1078,14 +1088,14 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APHOENIXLTD</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AGRASIM</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>LODHA</t>
+          <t>DMART</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1098,7 +1108,7 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bearish ND</t>
+          <t>Bullish ND</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -1108,14 +1118,14 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ALODHA</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ADMART</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>MAZDOCK</t>
+          <t>BANKINDIA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1138,14 +1148,14 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMAZDOCK</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABANKINDIA</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1168,14 +1178,14 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AITC</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHYUNDAI</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>RBLBANK</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1188,7 +1198,7 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bullish ND</t>
+          <t>Bearish ND</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -1198,14 +1208,14 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIGREEN</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ARBLBANK</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1228,14 +1238,14 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASIEMENS</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIENT</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>NATIONALUM</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1258,14 +1268,14 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANATIONALUM</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMFSL</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>PETRONET</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1288,14 +1298,14 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APETRONET</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APOWERGRID</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TATAMOTORS</t>
+          <t>CNXMIDCAP</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1318,14 +1328,14 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATATAMOTORS</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACNXMIDCAP</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1348,14 +1358,14 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APIDILITIND</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AITC</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1378,14 +1388,14 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATITAN</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIGREEN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>EXIDEIND</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1408,14 +1418,14 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AEXIDEIND</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASIEMENS</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>ADANIPOWER</t>
+          <t>TATAMOTORS</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1438,14 +1448,14 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIPOWER</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATATAMOTORS</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>BAJFINANCE</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1468,14 +1478,14 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABAJFINANCE</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AZYDUSLIFE</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ICICIPRULI</t>
+          <t>EXIDEIND</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1488,7 +1498,7 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bullish ND</t>
+          <t>Bearish ND</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -1498,14 +1508,14 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AICICIPRULI</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AEXIDEIND</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BSE</t>
+          <t>VOLTAS</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1528,14 +1538,14 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABSE</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AVOLTAS</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>SBIN</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1548,7 +1558,7 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bearish ND</t>
+          <t>Bullish ND</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -1558,7 +1568,307 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASBIN</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATATACONSUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>ABB</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABB</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>INDHOTEL</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AINDHOTEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>BANDHANBNK</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABANDHANBNK</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>NTPC</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Bullish ND</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANTPC</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>PREMIERENE</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APREMIERENE</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIPORTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>LICHSGFIN</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Bullish ND</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ALICHSGFIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABHEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AIDFCFIRSTB</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Bullish ND</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHEROMOTOCO</t>
         </is>
       </c>
     </row>
@@ -1573,66 +1883,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L42"/>
+  <dimension ref="A1:L33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Trend</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Setup</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Divergence</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Zone</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Confluence</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Bias</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>TV_Link</t>
         </is>
@@ -1641,7 +1951,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>CROMPTON</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1664,14 +1974,14 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACROMPTON</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANAUKRI</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>GMRAIRPORT</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1694,14 +2004,14 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANAUKRI</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AGMRAIRPORT</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>PFC</t>
+          <t>FORTIS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1714,7 +2024,7 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bullish ND</t>
+          <t>Bearish ND</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -1724,14 +2034,14 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APFC</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AFORTIS</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>YESBANK</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1744,7 +2054,7 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bullish ND</t>
+          <t>Bearish ND</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -1754,14 +2064,14 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AYESBANK</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACHOLAFIN</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BIOCON</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -1784,14 +2094,14 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABIOCON</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AJSWSTEEL</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>DRREDDY</t>
+          <t>PERSISTENT</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1814,14 +2124,14 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ADRREDDY</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APERSISTENT</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>PAYTM</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1834,7 +2144,7 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bullish ND</t>
+          <t>Bearish ND</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -1844,14 +2154,14 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANESTLEIND</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APAYTM</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>INOXWIND</t>
+          <t>UPL</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1874,14 +2184,14 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AINOXWIND</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AUPL</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>HDFCLIFE</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1904,14 +2214,14 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHDFCLIFE</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AFEDERALBNK</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SUZLON</t>
+          <t>WIPRO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1934,14 +2244,14 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASUZLON</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AWIPRO</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>PIIND</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1964,14 +2274,14 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAUROPHARMA</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APIIND</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>MARICO</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1994,14 +2304,14 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMARICO</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ALUPIN</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>TRENT</t>
+          <t>AUBANK</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2014,7 +2324,7 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bullish ND</t>
+          <t>Bearish ND</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -2024,14 +2334,14 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATRENT</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAUBANK</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>COLPAL</t>
+          <t>KAYNES</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2054,14 +2364,14 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACOLPAL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AKAYNES</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>SBICARD</t>
+          <t>KPITTECH</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2074,7 +2384,7 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bearish ND</t>
+          <t>Bullish ND</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -2084,14 +2394,14 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASBICARD</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AKPITTECH</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>HDFCBANK</t>
+          <t>TATAELXSI</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2114,14 +2424,14 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHDFCBANK</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATATAELXSI</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>COALINDIA</t>
+          <t>KALYANKJIL</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2144,14 +2454,14 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACOALINDIA</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AKALYANKJIL</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BAJAJ_AUTO</t>
+          <t>PGEL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2164,7 +2474,7 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bearish ND</t>
+          <t>Bullish ND</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2174,14 +2484,14 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABAJAJ_AUTO</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APGEL</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HAVELLS</t>
+          <t>CNXMIDCAP</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2194,7 +2504,7 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bullish ND</t>
+          <t>Bearish ND</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -2204,14 +2514,14 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHAVELLS</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACNXMIDCAP</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2224,7 +2534,7 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bearish ND</t>
+          <t>Bullish ND</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -2234,14 +2544,14 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AUNOMINDA</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AITC</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>NYKAA</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2254,7 +2564,7 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bearish ND</t>
+          <t>Bullish ND</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -2264,14 +2574,14 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANYKAA</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APIDILITIND</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BDL</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2284,7 +2594,7 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bullish ND</t>
+          <t>Bearish ND</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -2294,14 +2604,14 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABDL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATITAN</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2314,7 +2624,7 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bullish ND</t>
+          <t>Bearish ND</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -2324,14 +2634,14 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABEL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATATACONSUM</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>KALYANKJIL</t>
+          <t>SUPREMEIND</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2344,7 +2654,7 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bearish ND</t>
+          <t>Bullish ND</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -2354,14 +2664,14 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AKALYANKJIL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASUPREMEIND</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>VBL</t>
+          <t>IRFC</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2384,14 +2694,14 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AVBL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AIRFC</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TCS</t>
+          <t>TATASTEEL</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2414,14 +2724,14 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATCS</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATATASTEEL</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>POLICYBZR</t>
+          <t>INDIANB</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2434,7 +2744,7 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bullish ND</t>
+          <t>Bearish ND</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -2444,14 +2754,14 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APOLICYBZR</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AINDIANB</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TMPV</t>
+          <t>ABCAPITAL</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2464,7 +2774,7 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bullish ND</t>
+          <t>Bearish ND</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -2474,14 +2784,14 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATMPV</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABCAPITAL</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>MAZDOCK</t>
+          <t>BAJFINANCE</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2494,7 +2804,7 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bullish ND</t>
+          <t>Bearish ND</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -2504,14 +2814,14 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMAZDOCK</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABAJFINANCE</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>VOLTAS</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2524,7 +2834,7 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bearish ND</t>
+          <t>Bullish ND</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -2534,14 +2844,14 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AVOLTAS</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABHEL</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>INDUSTOWER</t>
+          <t>OIL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2564,14 +2874,14 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AINDUSTOWER</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AOIL</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>WAAREEENER</t>
+          <t>LTF</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2584,7 +2894,7 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bullish ND</t>
+          <t>Bearish ND</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -2594,277 +2904,7 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AWAAREEENER</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>LICI</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ALICI</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>JUBLFOOD</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Bullish ND</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AJUBLFOOD</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>DIVISLAB</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ADIVISLAB</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>UNITDSPR</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Bullish ND</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AUNITDSPR</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>TORNTPHARM</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATORNTPHARM</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>BANKBARODA</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Bullish ND</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABANKBARODA</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>INFY</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AINFY</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>IDFCFIRSTB</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Bullish ND</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AIDFCFIRSTB</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>PAGEIND</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Bullish ND</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APAGEIND</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ALTF</t>
         </is>
       </c>
     </row>
@@ -2879,66 +2919,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L47"/>
+  <dimension ref="A1:L45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" t="inlineStr">
+      <c r="A1" s="1" t="inlineStr">
         <is>
           <t>Symbol</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="B1" s="1" t="inlineStr">
         <is>
           <t>Signal</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="C1" s="1" t="inlineStr">
         <is>
           <t>Trend</t>
         </is>
       </c>
-      <c r="D1" t="inlineStr">
+      <c r="D1" s="1" t="inlineStr">
         <is>
           <t>State</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>Setup</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Divergence</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>RSI</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>Zone</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Confluence</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Bias</t>
         </is>
       </c>
-      <c r="K1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Probability</t>
         </is>
       </c>
-      <c r="L1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>TV_Link</t>
         </is>
@@ -2947,7 +2987,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SRF</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -2970,14 +3010,14 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASRF</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASAIL</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>ETERNAL</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2990,7 +3030,7 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bullish ND</t>
+          <t>Bearish ND</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -3000,14 +3040,14 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AIEX</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AETERNAL</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BIOCON</t>
+          <t>ANGELONE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3030,14 +3070,14 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABIOCON</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AANGELONE</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>INOXWIND</t>
+          <t>GMRAIRPORT</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3050,7 +3090,7 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bullish ND</t>
+          <t>Bearish ND</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -3060,14 +3100,14 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AINOXWIND</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AGMRAIRPORT</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>CHOLAFIN</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3090,14 +3130,14 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIENSOL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACHOLAFIN</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3120,14 +3160,14 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ALAURUSLABS</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANESTLEIND</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SWIGGY</t>
+          <t>LT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3140,7 +3180,7 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bullish ND</t>
+          <t>Bearish ND</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -3150,14 +3190,14 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASWIGGY</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ALT</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3170,7 +3210,7 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bullish ND</t>
+          <t>Bearish ND</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -3180,14 +3220,14 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AEICHERMOT</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAUROPHARMA</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3200,7 +3240,7 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bullish ND</t>
+          <t>Bearish ND</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -3210,14 +3250,14 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AICICIGI</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AM&amp;M</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SOLARINDS</t>
+          <t>BOSCHLTD</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3240,14 +3280,14 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASOLARINDS</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABOSCHLTD</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>APLAPOLLO</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3270,14 +3310,14 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AFEDERALBNK</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAPLAPOLLO</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PIIND</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3290,7 +3330,7 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bullish ND</t>
+          <t>Bearish ND</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -3300,14 +3340,14 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APIIND</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ARELIANCE</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>KEI</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3330,14 +3370,14 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMPHASIS</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AKEI</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BAJAJ_AUTO</t>
+          <t>ULTRACEMCO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3360,7 +3400,7 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABAJAJ_AUTO</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AULTRACEMCO</t>
         </is>
       </c>
     </row>
@@ -3397,7 +3437,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3420,14 +3460,14 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACOFORGE</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AUNOMINDA</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>JIOFIN</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3450,14 +3490,14 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AJIOFIN</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APOLYCAB</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3470,7 +3510,7 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bullish ND</t>
+          <t>Bearish ND</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -3480,14 +3520,14 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMCX</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACGPOWER</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>SUNPHARMA</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3510,14 +3550,14 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACGPOWER</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASUNPHARMA</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3540,14 +3580,14 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AGRASIM</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMOTHERSON</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DMART</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3560,7 +3600,7 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bullish ND</t>
+          <t>Bearish ND</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -3570,14 +3610,14 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ADMART</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AJINDALSTEL</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BANKINDIA</t>
+          <t>GRASIM</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3590,7 +3630,7 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bullish ND</t>
+          <t>Bearish ND</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -3600,14 +3640,14 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABANKINDIA</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AGRASIM</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>BANKINDIA</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3630,14 +3670,14 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHYUNDAI</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABANKINDIA</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>RBLBANK</t>
+          <t>LUPIN</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3660,14 +3700,14 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ARBLBANK</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ALUPIN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>CNXMIDCAP</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3690,14 +3730,14 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIENT</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACNXMIDCAP</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>PHOENIXLTD</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3710,7 +3750,7 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bullish ND</t>
+          <t>Bearish ND</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -3720,14 +3760,14 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMFSL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APHOENIXLTD</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>UNIONBANK</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3740,7 +3780,7 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bullish ND</t>
+          <t>Bearish ND</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -3750,14 +3790,14 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APOWERGRID</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AUNIONBANK</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CNXMIDCAP</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3780,14 +3820,14 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACNXMIDCAP</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATITAN</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>INDUSTOWER</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3800,7 +3840,7 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bullish ND</t>
+          <t>Bearish ND</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -3810,14 +3850,14 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AITC</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AINDUSTOWER</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3840,14 +3880,14 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIGREEN</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATATACONSUM</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>DALBHARAT</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3870,14 +3910,14 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASIEMENS</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ADALBHARAT</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TATAMOTORS</t>
+          <t>TECHM</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3890,7 +3930,7 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bullish ND</t>
+          <t>Bearish ND</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -3900,14 +3940,14 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATATAMOTORS</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATECHM</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>CANBK</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3930,14 +3970,14 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AZYDUSLIFE</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACANBK</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>EXIDEIND</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -3960,14 +4000,14 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AEXIDEIND</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIPORTS</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>VOLTAS</t>
+          <t>BANKBARODA</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -3980,7 +4020,7 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bullish ND</t>
+          <t>Bearish ND</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -3990,14 +4030,14 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AVOLTAS</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABANKBARODA</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>AXISBANK</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4010,7 +4050,7 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bullish ND</t>
+          <t>Bearish ND</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -4020,14 +4060,14 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATATACONSUM</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAXISBANK</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>ABB</t>
+          <t>BPCL</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4050,14 +4090,14 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABB</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABPCL</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>INDHOTEL</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4080,14 +4120,14 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AINDHOTEL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABHEL</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>BANDHANBNK</t>
+          <t>NMDC</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4110,14 +4150,14 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABANDHANBNK</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANMDC</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>NTPC</t>
+          <t>IDFCFIRSTB</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4130,7 +4170,7 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bullish ND</t>
+          <t>Bearish ND</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -4140,14 +4180,14 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANTPC</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AIDFCFIRSTB</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>PREMIERENE</t>
+          <t>NIFTY</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4170,14 +4210,14 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APREMIERENE</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANIFTY</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>HEROMOTOCO</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4200,14 +4240,14 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIPORTS</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHEROMOTOCO</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>LICHSGFIN</t>
+          <t>APOLLOHOSP</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4220,7 +4260,7 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bullish ND</t>
+          <t>Bearish ND</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -4230,14 +4270,14 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ALICHSGFIN</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAPOLLOHOSP</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>HINDPETRO</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4260,2498 +4300,6 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABHEL</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>IDFCFIRSTB</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AIDFCFIRSTB</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>HEROMOTOCO</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Bullish ND</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHEROMOTOCO</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L33"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Symbol</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Signal</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Trend</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>State</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Setup</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Divergence</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>RSI</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Zone</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Confluence</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Bias</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Probability</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>TV_Link</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>NAUKRI</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Bullish ND</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANAUKRI</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>GMRAIRPORT</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AGMRAIRPORT</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>FORTIS</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AFORTIS</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>CHOLAFIN</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACHOLAFIN</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>JSWSTEEL</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AJSWSTEEL</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>PERSISTENT</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Bullish ND</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APERSISTENT</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>PAYTM</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APAYTM</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>UPL</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Bullish ND</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AUPL</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>FEDERALBNK</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AFEDERALBNK</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>WIPRO</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Bullish ND</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AWIPRO</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>PIIND</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Bullish ND</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APIIND</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>LUPIN</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ALUPIN</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>AUBANK</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAUBANK</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>KAYNES</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Bullish ND</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AKAYNES</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>KPITTECH</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Bullish ND</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AKPITTECH</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>TATAELXSI</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Bullish ND</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATATAELXSI</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>KALYANKJIL</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Bullish ND</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AKALYANKJIL</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>PGEL</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Bullish ND</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APGEL</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>CNXMIDCAP</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACNXMIDCAP</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>ITC</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Bullish ND</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AITC</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>PIDILITIND</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Bullish ND</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APIDILITIND</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>TITAN</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATITAN</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>TATACONSUM</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATATACONSUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>SUPREMEIND</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Bullish ND</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASUPREMEIND</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>IRFC</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Bullish ND</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AIRFC</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>TATASTEEL</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATATASTEEL</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>INDIANB</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AINDIANB</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>ABCAPITAL</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABCAPITAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>BAJFINANCE</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABAJFINANCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>BHEL</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Bullish ND</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABHEL</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>OIL</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AOIL</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>LTF</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ALTF</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:L45"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>Symbol</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>Signal</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>Trend</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>State</t>
-        </is>
-      </c>
-      <c r="E1" t="inlineStr">
-        <is>
-          <t>Setup</t>
-        </is>
-      </c>
-      <c r="F1" t="inlineStr">
-        <is>
-          <t>Divergence</t>
-        </is>
-      </c>
-      <c r="G1" t="inlineStr">
-        <is>
-          <t>RSI</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>Zone</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>Confluence</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>Bias</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>Probability</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>TV_Link</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>SAIL</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="inlineStr"/>
-      <c r="E2" t="inlineStr"/>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr"/>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASAIL</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>ETERNAL</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="inlineStr"/>
-      <c r="E3" t="inlineStr"/>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr"/>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AETERNAL</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>ANGELONE</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="inlineStr"/>
-      <c r="E4" t="inlineStr"/>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr"/>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
-      <c r="L4" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AANGELONE</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>GMRAIRPORT</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="inlineStr"/>
-      <c r="E5" t="inlineStr"/>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AGMRAIRPORT</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>CHOLAFIN</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACHOLAFIN</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>NESTLEIND</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr"/>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
-      <c r="J7" t="inlineStr"/>
-      <c r="K7" t="inlineStr"/>
-      <c r="L7" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANESTLEIND</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>LT</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr"/>
-      <c r="D8" t="inlineStr"/>
-      <c r="E8" t="inlineStr"/>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr"/>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
-      <c r="J8" t="inlineStr"/>
-      <c r="K8" t="inlineStr"/>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ALT</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>AUROPHARMA</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr"/>
-      <c r="D9" t="inlineStr"/>
-      <c r="E9" t="inlineStr"/>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr"/>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
-      <c r="J9" t="inlineStr"/>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAUROPHARMA</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>M&amp;M</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr"/>
-      <c r="E10" t="inlineStr"/>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr"/>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr"/>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AM&amp;M</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>BOSCHLTD</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr"/>
-      <c r="D11" t="inlineStr"/>
-      <c r="E11" t="inlineStr"/>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr"/>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr"/>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABOSCHLTD</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>APLAPOLLO</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr"/>
-      <c r="D12" t="inlineStr"/>
-      <c r="E12" t="inlineStr"/>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr"/>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
-      <c r="J12" t="inlineStr"/>
-      <c r="K12" t="inlineStr"/>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAPLAPOLLO</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>RELIANCE</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr"/>
-      <c r="D13" t="inlineStr"/>
-      <c r="E13" t="inlineStr"/>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr"/>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
-      <c r="J13" t="inlineStr"/>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ARELIANCE</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>KEI</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr"/>
-      <c r="D14" t="inlineStr"/>
-      <c r="E14" t="inlineStr"/>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr"/>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
-      <c r="J14" t="inlineStr"/>
-      <c r="K14" t="inlineStr"/>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AKEI</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>ULTRACEMCO</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr"/>
-      <c r="D15" t="inlineStr"/>
-      <c r="E15" t="inlineStr"/>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr"/>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
-      <c r="J15" t="inlineStr"/>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AULTRACEMCO</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>MOTILALOFS</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-      <c r="E16" t="inlineStr"/>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr"/>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
-      <c r="J16" t="inlineStr"/>
-      <c r="K16" t="inlineStr"/>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMOTILALOFS</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>UNOMINDA</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
-      <c r="E17" t="inlineStr"/>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr"/>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
-      <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr"/>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AUNOMINDA</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>POLYCAB</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
-      <c r="E18" t="inlineStr"/>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr"/>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
-      <c r="J18" t="inlineStr"/>
-      <c r="K18" t="inlineStr"/>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APOLYCAB</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>CGPOWER</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
-      <c r="E19" t="inlineStr"/>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr"/>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
-      <c r="J19" t="inlineStr"/>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACGPOWER</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>SUNPHARMA</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
-      <c r="E20" t="inlineStr"/>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr"/>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
-      <c r="J20" t="inlineStr"/>
-      <c r="K20" t="inlineStr"/>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASUNPHARMA</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>MOTHERSON</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
-      <c r="E21" t="inlineStr"/>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr"/>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
-      <c r="J21" t="inlineStr"/>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMOTHERSON</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>JINDALSTEL</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
-      <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr"/>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
-      <c r="J22" t="inlineStr"/>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AJINDALSTEL</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>GRASIM</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
-      <c r="E23" t="inlineStr"/>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr"/>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
-      <c r="J23" t="inlineStr"/>
-      <c r="K23" t="inlineStr"/>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AGRASIM</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>BANKINDIA</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr"/>
-      <c r="D24" t="inlineStr"/>
-      <c r="E24" t="inlineStr"/>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr"/>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
-      <c r="J24" t="inlineStr"/>
-      <c r="K24" t="inlineStr"/>
-      <c r="L24" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABANKINDIA</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>LUPIN</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr"/>
-      <c r="D25" t="inlineStr"/>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr"/>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
-      <c r="J25" t="inlineStr"/>
-      <c r="K25" t="inlineStr"/>
-      <c r="L25" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ALUPIN</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>CNXMIDCAP</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr"/>
-      <c r="D26" t="inlineStr"/>
-      <c r="E26" t="inlineStr"/>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr"/>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
-      <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr"/>
-      <c r="L26" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACNXMIDCAP</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>PHOENIXLTD</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr"/>
-      <c r="D27" t="inlineStr"/>
-      <c r="E27" t="inlineStr"/>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr"/>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
-      <c r="J27" t="inlineStr"/>
-      <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APHOENIXLTD</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>UNIONBANK</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr"/>
-      <c r="D28" t="inlineStr"/>
-      <c r="E28" t="inlineStr"/>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr"/>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
-      <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr"/>
-      <c r="L28" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AUNIONBANK</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>TITAN</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr"/>
-      <c r="D29" t="inlineStr"/>
-      <c r="E29" t="inlineStr"/>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr"/>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
-      <c r="J29" t="inlineStr"/>
-      <c r="K29" t="inlineStr"/>
-      <c r="L29" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATITAN</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>INDUSTOWER</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr"/>
-      <c r="D30" t="inlineStr"/>
-      <c r="E30" t="inlineStr"/>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr"/>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
-      <c r="J30" t="inlineStr"/>
-      <c r="K30" t="inlineStr"/>
-      <c r="L30" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AINDUSTOWER</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>TATACONSUM</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr"/>
-      <c r="D31" t="inlineStr"/>
-      <c r="E31" t="inlineStr"/>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr"/>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
-      <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr"/>
-      <c r="L31" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATATACONSUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>DALBHARAT</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr"/>
-      <c r="D32" t="inlineStr"/>
-      <c r="E32" t="inlineStr"/>
-      <c r="F32" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G32" t="inlineStr"/>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
-      <c r="J32" t="inlineStr"/>
-      <c r="K32" t="inlineStr"/>
-      <c r="L32" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ADALBHARAT</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>TECHM</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr"/>
-      <c r="D33" t="inlineStr"/>
-      <c r="E33" t="inlineStr"/>
-      <c r="F33" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G33" t="inlineStr"/>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
-      <c r="J33" t="inlineStr"/>
-      <c r="K33" t="inlineStr"/>
-      <c r="L33" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATECHM</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>CANBK</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr"/>
-      <c r="D34" t="inlineStr"/>
-      <c r="E34" t="inlineStr"/>
-      <c r="F34" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G34" t="inlineStr"/>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
-      <c r="J34" t="inlineStr"/>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACANBK</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>ADANIPORTS</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr"/>
-      <c r="D35" t="inlineStr"/>
-      <c r="E35" t="inlineStr"/>
-      <c r="F35" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G35" t="inlineStr"/>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
-      <c r="J35" t="inlineStr"/>
-      <c r="K35" t="inlineStr"/>
-      <c r="L35" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIPORTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>BANKBARODA</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr"/>
-      <c r="D36" t="inlineStr"/>
-      <c r="E36" t="inlineStr"/>
-      <c r="F36" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G36" t="inlineStr"/>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
-      <c r="J36" t="inlineStr"/>
-      <c r="K36" t="inlineStr"/>
-      <c r="L36" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABANKBARODA</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>AXISBANK</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr"/>
-      <c r="D37" t="inlineStr"/>
-      <c r="E37" t="inlineStr"/>
-      <c r="F37" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G37" t="inlineStr"/>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
-      <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr"/>
-      <c r="L37" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAXISBANK</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>BPCL</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABPCL</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>BHEL</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABHEL</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>NMDC</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANMDC</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>IDFCFIRSTB</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AIDFCFIRSTB</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>NIFTY</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANIFTY</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>HEROMOTOCO</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHEROMOTOCO</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>APOLLOHOSP</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAPOLLOHOSP</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>HINDPETRO</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr">
-        <is>
           <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHINDPETRO</t>
         </is>
       </c>

--- a/Output/MACD Normal Divergences_19 Jul 2026.xlsx
+++ b/Output/MACD Normal Divergences_19 Jul 2026.xlsx
@@ -7,9 +7,11 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Daily" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Weekly" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Monthly" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="15 Min" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Hourly" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Daily" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Weekly" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Monthly" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -427,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L47"/>
+  <dimension ref="A1:L37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -495,7 +497,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SRF</t>
+          <t>PATANJALI</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -508,7 +510,7 @@
       <c r="E2" t="inlineStr"/>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Bearish ND</t>
+          <t>Bullish ND</t>
         </is>
       </c>
       <c r="G2" t="inlineStr"/>
@@ -518,14 +520,14 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASRF</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APATANJALI</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>IEX</t>
+          <t>SUZLON</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -548,14 +550,14 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AIEX</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASUZLON</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BIOCON</t>
+          <t>JSWSTEEL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -568,7 +570,7 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bearish ND</t>
+          <t>Bullish ND</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -578,14 +580,14 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABIOCON</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AJSWSTEEL</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>INOXWIND</t>
+          <t>M&amp;M</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -598,7 +600,7 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bullish ND</t>
+          <t>Bearish ND</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -608,14 +610,14 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AINOXWIND</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AM&amp;M</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>ADANIENSOL</t>
+          <t>INDUSINDBK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -638,14 +640,14 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIENSOL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AINDUSINDBK</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>LAURUSLABS</t>
+          <t>SWIGGY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -668,14 +670,14 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ALAURUSLABS</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASWIGGY</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>SWIGGY</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -688,7 +690,7 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bullish ND</t>
+          <t>Bearish ND</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -698,14 +700,14 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASWIGGY</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AEICHERMOT</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>EICHERMOT</t>
+          <t>TRENT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -728,14 +730,14 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AEICHERMOT</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATRENT</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ICICIGI</t>
+          <t>RELIANCE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -748,7 +750,7 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bullish ND</t>
+          <t>Bearish ND</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -758,14 +760,14 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AICICIGI</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ARELIANCE</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>SOLARINDS</t>
+          <t>KEI</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -778,7 +780,7 @@
       <c r="E11" t="inlineStr"/>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bearish ND</t>
+          <t>Bullish ND</t>
         </is>
       </c>
       <c r="G11" t="inlineStr"/>
@@ -788,7 +790,7 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASOLARINDS</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AKEI</t>
         </is>
       </c>
     </row>
@@ -808,7 +810,7 @@
       <c r="E12" t="inlineStr"/>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bearish ND</t>
+          <t>Bullish ND</t>
         </is>
       </c>
       <c r="G12" t="inlineStr"/>
@@ -825,7 +827,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>PIIND</t>
+          <t>HAVELLS</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -848,14 +850,14 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APIIND</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHAVELLS</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>MPHASIS</t>
+          <t>POLYCAB</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -868,7 +870,7 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bearish ND</t>
+          <t>Bullish ND</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -878,14 +880,14 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMPHASIS</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APOLYCAB</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BAJAJ_AUTO</t>
+          <t>MOTHERSON</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -908,14 +910,14 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABAJAJ_AUTO</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMOTHERSON</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>MOTILALOFS</t>
+          <t>JINDALSTEL</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -928,7 +930,7 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bearish ND</t>
+          <t>Bullish ND</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -938,14 +940,14 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMOTILALOFS</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AJINDALSTEL</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>COFORGE</t>
+          <t>BDL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -958,7 +960,7 @@
       <c r="E17" t="inlineStr"/>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Bearish ND</t>
+          <t>Bullish ND</t>
         </is>
       </c>
       <c r="G17" t="inlineStr"/>
@@ -968,14 +970,14 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACOFORGE</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABDL</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>JIOFIN</t>
+          <t>AUBANK</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -988,7 +990,7 @@
       <c r="E18" t="inlineStr"/>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Bearish ND</t>
+          <t>Bullish ND</t>
         </is>
       </c>
       <c r="G18" t="inlineStr"/>
@@ -998,14 +1000,14 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AJIOFIN</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAUBANK</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MCX</t>
+          <t>TATAELXSI</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1028,14 +1030,14 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMCX</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATATAELXSI</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>BLUESTARCO</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1048,7 +1050,7 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bearish ND</t>
+          <t>Bullish ND</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -1058,14 +1060,14 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACGPOWER</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABLUESTARCO</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>PHOENIXLTD</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -1078,7 +1080,7 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bearish ND</t>
+          <t>Bullish ND</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -1088,14 +1090,14 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AGRASIM</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APHOENIXLTD</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>DMART</t>
+          <t>LODHA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1108,7 +1110,7 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bullish ND</t>
+          <t>Bearish ND</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -1118,14 +1120,14 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ADMART</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ALODHA</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BANKINDIA</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1148,14 +1150,14 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABANKINDIA</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMAZDOCK</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>HYUNDAI</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1178,14 +1180,14 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHYUNDAI</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AITC</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>RBLBANK</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -1198,7 +1200,7 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bearish ND</t>
+          <t>Bullish ND</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -1208,14 +1210,14 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ARBLBANK</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIGREEN</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>ADANIENT</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1238,14 +1240,14 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIENT</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASIEMENS</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>MFSL</t>
+          <t>NATIONALUM</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1268,14 +1270,14 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMFSL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANATIONALUM</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>POWERGRID</t>
+          <t>PETRONET</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1298,14 +1300,14 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APOWERGRID</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APETRONET</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>CNXMIDCAP</t>
+          <t>TATAMOTORS</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1328,14 +1330,14 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACNXMIDCAP</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATATAMOTORS</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>PIDILITIND</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -1358,14 +1360,14 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AITC</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APIDILITIND</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>ADANIGREEN</t>
+          <t>TITAN</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1388,14 +1390,14 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIGREEN</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATITAN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>SIEMENS</t>
+          <t>EXIDEIND</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1418,14 +1420,14 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASIEMENS</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AEXIDEIND</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TATAMOTORS</t>
+          <t>ADANIPOWER</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -1448,14 +1450,14 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATATAMOTORS</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIPOWER</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>ZYDUSLIFE</t>
+          <t>BAJFINANCE</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1478,14 +1480,14 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AZYDUSLIFE</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABAJFINANCE</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>EXIDEIND</t>
+          <t>ICICIPRULI</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -1498,7 +1500,7 @@
       <c r="E35" t="inlineStr"/>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Bearish ND</t>
+          <t>Bullish ND</t>
         </is>
       </c>
       <c r="G35" t="inlineStr"/>
@@ -1508,14 +1510,14 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AEXIDEIND</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AICICIPRULI</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>VOLTAS</t>
+          <t>BSE</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1538,14 +1540,14 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AVOLTAS</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABSE</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>SBIN</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -1558,7 +1560,7 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bullish ND</t>
+          <t>Bearish ND</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -1568,307 +1570,7 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATATACONSUM</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>ABB</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr"/>
-      <c r="D38" t="inlineStr"/>
-      <c r="E38" t="inlineStr"/>
-      <c r="F38" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G38" t="inlineStr"/>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
-      <c r="J38" t="inlineStr"/>
-      <c r="K38" t="inlineStr"/>
-      <c r="L38" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABB</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>INDHOTEL</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr"/>
-      <c r="D39" t="inlineStr"/>
-      <c r="E39" t="inlineStr"/>
-      <c r="F39" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G39" t="inlineStr"/>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
-      <c r="J39" t="inlineStr"/>
-      <c r="K39" t="inlineStr"/>
-      <c r="L39" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AINDHOTEL</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>BANDHANBNK</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr"/>
-      <c r="D40" t="inlineStr"/>
-      <c r="E40" t="inlineStr"/>
-      <c r="F40" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G40" t="inlineStr"/>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
-      <c r="J40" t="inlineStr"/>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABANDHANBNK</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>NTPC</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C41" t="inlineStr"/>
-      <c r="D41" t="inlineStr"/>
-      <c r="E41" t="inlineStr"/>
-      <c r="F41" t="inlineStr">
-        <is>
-          <t>Bullish ND</t>
-        </is>
-      </c>
-      <c r="G41" t="inlineStr"/>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
-      <c r="J41" t="inlineStr"/>
-      <c r="K41" t="inlineStr"/>
-      <c r="L41" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANTPC</t>
-        </is>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>PREMIERENE</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C42" t="inlineStr"/>
-      <c r="D42" t="inlineStr"/>
-      <c r="E42" t="inlineStr"/>
-      <c r="F42" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G42" t="inlineStr"/>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
-      <c r="J42" t="inlineStr"/>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APREMIERENE</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>ADANIPORTS</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C43" t="inlineStr"/>
-      <c r="D43" t="inlineStr"/>
-      <c r="E43" t="inlineStr"/>
-      <c r="F43" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G43" t="inlineStr"/>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
-      <c r="J43" t="inlineStr"/>
-      <c r="K43" t="inlineStr"/>
-      <c r="L43" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIPORTS</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>LICHSGFIN</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C44" t="inlineStr"/>
-      <c r="D44" t="inlineStr"/>
-      <c r="E44" t="inlineStr"/>
-      <c r="F44" t="inlineStr">
-        <is>
-          <t>Bullish ND</t>
-        </is>
-      </c>
-      <c r="G44" t="inlineStr"/>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
-      <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr"/>
-      <c r="L44" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ALICHSGFIN</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>BHEL</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C45" t="inlineStr"/>
-      <c r="D45" t="inlineStr"/>
-      <c r="E45" t="inlineStr"/>
-      <c r="F45" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G45" t="inlineStr"/>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
-      <c r="J45" t="inlineStr"/>
-      <c r="K45" t="inlineStr"/>
-      <c r="L45" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABHEL</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>IDFCFIRSTB</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr"/>
-      <c r="D46" t="inlineStr"/>
-      <c r="E46" t="inlineStr"/>
-      <c r="F46" t="inlineStr">
-        <is>
-          <t>Bearish ND</t>
-        </is>
-      </c>
-      <c r="G46" t="inlineStr"/>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
-      <c r="J46" t="inlineStr"/>
-      <c r="K46" t="inlineStr"/>
-      <c r="L46" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AIDFCFIRSTB</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>HEROMOTOCO</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Divergence Alert</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr"/>
-      <c r="D47" t="inlineStr"/>
-      <c r="E47" t="inlineStr"/>
-      <c r="F47" t="inlineStr">
-        <is>
-          <t>Bullish ND</t>
-        </is>
-      </c>
-      <c r="G47" t="inlineStr"/>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
-      <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr"/>
-      <c r="L47" t="inlineStr">
-        <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHEROMOTOCO</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASBIN</t>
         </is>
       </c>
     </row>
@@ -1883,7 +1585,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L33"/>
+  <dimension ref="A1:L42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1951,7 +1653,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>NAUKRI</t>
+          <t>CROMPTON</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1974,14 +1676,14 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANAUKRI</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACROMPTON</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>GMRAIRPORT</t>
+          <t>NAUKRI</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -2004,14 +1706,14 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AGMRAIRPORT</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANAUKRI</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>FORTIS</t>
+          <t>PFC</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2024,7 +1726,7 @@
       <c r="E4" t="inlineStr"/>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Bearish ND</t>
+          <t>Bullish ND</t>
         </is>
       </c>
       <c r="G4" t="inlineStr"/>
@@ -2034,14 +1736,14 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AFORTIS</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APFC</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>YESBANK</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2054,7 +1756,7 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bearish ND</t>
+          <t>Bullish ND</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -2064,14 +1766,14 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACHOLAFIN</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AYESBANK</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>JSWSTEEL</t>
+          <t>BIOCON</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2094,14 +1796,14 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AJSWSTEEL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABIOCON</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>PERSISTENT</t>
+          <t>DRREDDY</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -2124,14 +1826,14 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APERSISTENT</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ADRREDDY</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>PAYTM</t>
+          <t>NESTLEIND</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -2144,7 +1846,7 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bearish ND</t>
+          <t>Bullish ND</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -2154,14 +1856,14 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APAYTM</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANESTLEIND</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>UPL</t>
+          <t>INOXWIND</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -2184,14 +1886,14 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AUPL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AINOXWIND</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>FEDERALBNK</t>
+          <t>HDFCLIFE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -2214,14 +1916,14 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AFEDERALBNK</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHDFCLIFE</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>WIPRO</t>
+          <t>SUZLON</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -2244,14 +1946,14 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AWIPRO</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASUZLON</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>PIIND</t>
+          <t>AUROPHARMA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -2274,14 +1976,14 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APIIND</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAUROPHARMA</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>MARICO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -2304,14 +2006,14 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ALUPIN</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMARICO</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AUBANK</t>
+          <t>TRENT</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -2324,7 +2026,7 @@
       <c r="E14" t="inlineStr"/>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bearish ND</t>
+          <t>Bullish ND</t>
         </is>
       </c>
       <c r="G14" t="inlineStr"/>
@@ -2334,14 +2036,14 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAUBANK</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATRENT</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>KAYNES</t>
+          <t>COLPAL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -2364,14 +2066,14 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AKAYNES</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACOLPAL</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>KPITTECH</t>
+          <t>SBICARD</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -2384,7 +2086,7 @@
       <c r="E16" t="inlineStr"/>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Bullish ND</t>
+          <t>Bearish ND</t>
         </is>
       </c>
       <c r="G16" t="inlineStr"/>
@@ -2394,14 +2096,14 @@
       <c r="K16" t="inlineStr"/>
       <c r="L16" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AKPITTECH</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASBICARD</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>TATAELXSI</t>
+          <t>HDFCBANK</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -2424,14 +2126,14 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATATAELXSI</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHDFCBANK</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>KALYANKJIL</t>
+          <t>COALINDIA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -2454,14 +2156,14 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AKALYANKJIL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACOALINDIA</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>PGEL</t>
+          <t>BAJAJ_AUTO</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -2474,7 +2176,7 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bullish ND</t>
+          <t>Bearish ND</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -2484,14 +2186,14 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APGEL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABAJAJ_AUTO</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>CNXMIDCAP</t>
+          <t>HAVELLS</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -2504,7 +2206,7 @@
       <c r="E20" t="inlineStr"/>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bearish ND</t>
+          <t>Bullish ND</t>
         </is>
       </c>
       <c r="G20" t="inlineStr"/>
@@ -2514,14 +2216,14 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACNXMIDCAP</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHAVELLS</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>ITC</t>
+          <t>UNOMINDA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2534,7 +2236,7 @@
       <c r="E21" t="inlineStr"/>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Bullish ND</t>
+          <t>Bearish ND</t>
         </is>
       </c>
       <c r="G21" t="inlineStr"/>
@@ -2544,14 +2246,14 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AITC</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AUNOMINDA</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>PIDILITIND</t>
+          <t>NYKAA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2564,7 +2266,7 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bullish ND</t>
+          <t>Bearish ND</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -2574,14 +2276,14 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APIDILITIND</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANYKAA</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>BDL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2594,7 +2296,7 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bearish ND</t>
+          <t>Bullish ND</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -2604,14 +2306,14 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATITAN</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABDL</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2624,7 +2326,7 @@
       <c r="E24" t="inlineStr"/>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Bearish ND</t>
+          <t>Bullish ND</t>
         </is>
       </c>
       <c r="G24" t="inlineStr"/>
@@ -2634,14 +2336,14 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATATACONSUM</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABEL</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>SUPREMEIND</t>
+          <t>KALYANKJIL</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2654,7 +2356,7 @@
       <c r="E25" t="inlineStr"/>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Bullish ND</t>
+          <t>Bearish ND</t>
         </is>
       </c>
       <c r="G25" t="inlineStr"/>
@@ -2664,14 +2366,14 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASUPREMEIND</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AKALYANKJIL</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>IRFC</t>
+          <t>VBL</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -2694,14 +2396,14 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AIRFC</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AVBL</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>TATASTEEL</t>
+          <t>TCS</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -2724,14 +2426,14 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATATASTEEL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATCS</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>INDIANB</t>
+          <t>POLICYBZR</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -2744,7 +2446,7 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bearish ND</t>
+          <t>Bullish ND</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -2754,14 +2456,14 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AINDIANB</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APOLICYBZR</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>ABCAPITAL</t>
+          <t>TMPV</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -2774,7 +2476,7 @@
       <c r="E29" t="inlineStr"/>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Bearish ND</t>
+          <t>Bullish ND</t>
         </is>
       </c>
       <c r="G29" t="inlineStr"/>
@@ -2784,14 +2486,14 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABCAPITAL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATMPV</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BAJFINANCE</t>
+          <t>MAZDOCK</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -2804,7 +2506,7 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bearish ND</t>
+          <t>Bullish ND</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -2814,14 +2516,14 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABAJFINANCE</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMAZDOCK</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>VOLTAS</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -2834,7 +2536,7 @@
       <c r="E31" t="inlineStr"/>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Bullish ND</t>
+          <t>Bearish ND</t>
         </is>
       </c>
       <c r="G31" t="inlineStr"/>
@@ -2844,14 +2546,14 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABHEL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AVOLTAS</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>OIL</t>
+          <t>INDUSTOWER</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -2874,14 +2576,14 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AOIL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AINDUSTOWER</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>LTF</t>
+          <t>WAAREEENER</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -2894,7 +2596,7 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bearish ND</t>
+          <t>Bullish ND</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -2904,7 +2606,277 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ALTF</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AWAAREEENER</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>LICI</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ALICI</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>JUBLFOOD</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Bullish ND</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AJUBLFOOD</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>DIVISLAB</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ADIVISLAB</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>UNITDSPR</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Bullish ND</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AUNITDSPR</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>TORNTPHARM</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATORNTPHARM</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>BANKBARODA</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Bullish ND</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABANKBARODA</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>INFY</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AINFY</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Bullish ND</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AIDFCFIRSTB</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>PAGEIND</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Bullish ND</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APAGEIND</t>
         </is>
       </c>
     </row>
@@ -2919,7 +2891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L45"/>
+  <dimension ref="A1:L47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2987,7 +2959,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>SAIL</t>
+          <t>SRF</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -3010,14 +2982,14 @@
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASAIL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASRF</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>ETERNAL</t>
+          <t>IEX</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -3030,7 +3002,7 @@
       <c r="E3" t="inlineStr"/>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Bearish ND</t>
+          <t>Bullish ND</t>
         </is>
       </c>
       <c r="G3" t="inlineStr"/>
@@ -3040,14 +3012,14 @@
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AETERNAL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AIEX</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>ANGELONE</t>
+          <t>BIOCON</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -3070,14 +3042,14 @@
       <c r="K4" t="inlineStr"/>
       <c r="L4" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AANGELONE</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABIOCON</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GMRAIRPORT</t>
+          <t>INOXWIND</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3090,7 +3062,7 @@
       <c r="E5" t="inlineStr"/>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bearish ND</t>
+          <t>Bullish ND</t>
         </is>
       </c>
       <c r="G5" t="inlineStr"/>
@@ -3100,14 +3072,14 @@
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AGMRAIRPORT</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AINOXWIND</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>CHOLAFIN</t>
+          <t>ADANIENSOL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -3130,14 +3102,14 @@
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACHOLAFIN</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIENSOL</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NESTLEIND</t>
+          <t>LAURUSLABS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3160,14 +3132,14 @@
       <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANESTLEIND</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ALAURUSLABS</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>LT</t>
+          <t>SWIGGY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3180,7 +3152,7 @@
       <c r="E8" t="inlineStr"/>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bearish ND</t>
+          <t>Bullish ND</t>
         </is>
       </c>
       <c r="G8" t="inlineStr"/>
@@ -3190,14 +3162,14 @@
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ALT</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASWIGGY</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AUROPHARMA</t>
+          <t>EICHERMOT</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -3210,7 +3182,7 @@
       <c r="E9" t="inlineStr"/>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Bearish ND</t>
+          <t>Bullish ND</t>
         </is>
       </c>
       <c r="G9" t="inlineStr"/>
@@ -3220,14 +3192,14 @@
       <c r="K9" t="inlineStr"/>
       <c r="L9" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAUROPHARMA</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AEICHERMOT</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M&amp;M</t>
+          <t>ICICIGI</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3240,7 +3212,7 @@
       <c r="E10" t="inlineStr"/>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bearish ND</t>
+          <t>Bullish ND</t>
         </is>
       </c>
       <c r="G10" t="inlineStr"/>
@@ -3250,14 +3222,14 @@
       <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AM&amp;M</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AICICIGI</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>BOSCHLTD</t>
+          <t>SOLARINDS</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3280,14 +3252,14 @@
       <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABOSCHLTD</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASOLARINDS</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>APLAPOLLO</t>
+          <t>FEDERALBNK</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -3310,14 +3282,14 @@
       <c r="K12" t="inlineStr"/>
       <c r="L12" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAPLAPOLLO</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AFEDERALBNK</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>RELIANCE</t>
+          <t>PIIND</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3330,7 +3302,7 @@
       <c r="E13" t="inlineStr"/>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bearish ND</t>
+          <t>Bullish ND</t>
         </is>
       </c>
       <c r="G13" t="inlineStr"/>
@@ -3340,14 +3312,14 @@
       <c r="K13" t="inlineStr"/>
       <c r="L13" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ARELIANCE</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APIIND</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>KEI</t>
+          <t>MPHASIS</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -3370,14 +3342,14 @@
       <c r="K14" t="inlineStr"/>
       <c r="L14" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AKEI</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMPHASIS</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>ULTRACEMCO</t>
+          <t>BAJAJ_AUTO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -3400,7 +3372,7 @@
       <c r="K15" t="inlineStr"/>
       <c r="L15" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AULTRACEMCO</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABAJAJ_AUTO</t>
         </is>
       </c>
     </row>
@@ -3437,7 +3409,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>UNOMINDA</t>
+          <t>COFORGE</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -3460,14 +3432,14 @@
       <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AUNOMINDA</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACOFORGE</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>POLYCAB</t>
+          <t>JIOFIN</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -3490,14 +3462,14 @@
       <c r="K18" t="inlineStr"/>
       <c r="L18" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APOLYCAB</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AJIOFIN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>CGPOWER</t>
+          <t>MCX</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -3510,7 +3482,7 @@
       <c r="E19" t="inlineStr"/>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Bearish ND</t>
+          <t>Bullish ND</t>
         </is>
       </c>
       <c r="G19" t="inlineStr"/>
@@ -3520,14 +3492,14 @@
       <c r="K19" t="inlineStr"/>
       <c r="L19" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACGPOWER</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMCX</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>SUNPHARMA</t>
+          <t>CGPOWER</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -3550,14 +3522,14 @@
       <c r="K20" t="inlineStr"/>
       <c r="L20" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASUNPHARMA</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACGPOWER</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>MOTHERSON</t>
+          <t>GRASIM</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -3580,14 +3552,14 @@
       <c r="K21" t="inlineStr"/>
       <c r="L21" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMOTHERSON</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AGRASIM</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>JINDALSTEL</t>
+          <t>DMART</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -3600,7 +3572,7 @@
       <c r="E22" t="inlineStr"/>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Bearish ND</t>
+          <t>Bullish ND</t>
         </is>
       </c>
       <c r="G22" t="inlineStr"/>
@@ -3610,14 +3582,14 @@
       <c r="K22" t="inlineStr"/>
       <c r="L22" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AJINDALSTEL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ADMART</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>GRASIM</t>
+          <t>BANKINDIA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -3630,7 +3602,7 @@
       <c r="E23" t="inlineStr"/>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bearish ND</t>
+          <t>Bullish ND</t>
         </is>
       </c>
       <c r="G23" t="inlineStr"/>
@@ -3640,14 +3612,14 @@
       <c r="K23" t="inlineStr"/>
       <c r="L23" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AGRASIM</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABANKINDIA</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BANKINDIA</t>
+          <t>HYUNDAI</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -3670,14 +3642,14 @@
       <c r="K24" t="inlineStr"/>
       <c r="L24" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABANKINDIA</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHYUNDAI</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LUPIN</t>
+          <t>RBLBANK</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -3700,14 +3672,14 @@
       <c r="K25" t="inlineStr"/>
       <c r="L25" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ALUPIN</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ARBLBANK</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>CNXMIDCAP</t>
+          <t>ADANIENT</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -3730,14 +3702,14 @@
       <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACNXMIDCAP</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIENT</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>PHOENIXLTD</t>
+          <t>MFSL</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -3750,7 +3722,7 @@
       <c r="E27" t="inlineStr"/>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Bearish ND</t>
+          <t>Bullish ND</t>
         </is>
       </c>
       <c r="G27" t="inlineStr"/>
@@ -3760,14 +3732,14 @@
       <c r="K27" t="inlineStr"/>
       <c r="L27" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APHOENIXLTD</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMFSL</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>UNIONBANK</t>
+          <t>POWERGRID</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -3780,7 +3752,7 @@
       <c r="E28" t="inlineStr"/>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Bearish ND</t>
+          <t>Bullish ND</t>
         </is>
       </c>
       <c r="G28" t="inlineStr"/>
@@ -3790,14 +3762,14 @@
       <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AUNIONBANK</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APOWERGRID</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TITAN</t>
+          <t>CNXMIDCAP</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -3820,14 +3792,14 @@
       <c r="K29" t="inlineStr"/>
       <c r="L29" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATITAN</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACNXMIDCAP</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>INDUSTOWER</t>
+          <t>ITC</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -3840,7 +3812,7 @@
       <c r="E30" t="inlineStr"/>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Bearish ND</t>
+          <t>Bullish ND</t>
         </is>
       </c>
       <c r="G30" t="inlineStr"/>
@@ -3850,14 +3822,14 @@
       <c r="K30" t="inlineStr"/>
       <c r="L30" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AINDUSTOWER</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AITC</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>TATACONSUM</t>
+          <t>ADANIGREEN</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -3880,14 +3852,14 @@
       <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATATACONSUM</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIGREEN</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>DALBHARAT</t>
+          <t>SIEMENS</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -3910,14 +3882,14 @@
       <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ADALBHARAT</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASIEMENS</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TECHM</t>
+          <t>TATAMOTORS</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -3930,7 +3902,7 @@
       <c r="E33" t="inlineStr"/>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Bearish ND</t>
+          <t>Bullish ND</t>
         </is>
       </c>
       <c r="G33" t="inlineStr"/>
@@ -3940,14 +3912,14 @@
       <c r="K33" t="inlineStr"/>
       <c r="L33" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATECHM</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATATAMOTORS</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CANBK</t>
+          <t>ZYDUSLIFE</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -3970,14 +3942,14 @@
       <c r="K34" t="inlineStr"/>
       <c r="L34" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACANBK</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AZYDUSLIFE</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>ADANIPORTS</t>
+          <t>EXIDEIND</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -4000,14 +3972,14 @@
       <c r="K35" t="inlineStr"/>
       <c r="L35" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIPORTS</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AEXIDEIND</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>BANKBARODA</t>
+          <t>VOLTAS</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -4020,7 +3992,7 @@
       <c r="E36" t="inlineStr"/>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Bearish ND</t>
+          <t>Bullish ND</t>
         </is>
       </c>
       <c r="G36" t="inlineStr"/>
@@ -4030,14 +4002,14 @@
       <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABANKBARODA</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AVOLTAS</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>AXISBANK</t>
+          <t>TATACONSUM</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -4050,7 +4022,7 @@
       <c r="E37" t="inlineStr"/>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Bearish ND</t>
+          <t>Bullish ND</t>
         </is>
       </c>
       <c r="G37" t="inlineStr"/>
@@ -4060,14 +4032,14 @@
       <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAXISBANK</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATATACONSUM</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>BPCL</t>
+          <t>ABB</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -4090,14 +4062,14 @@
       <c r="K38" t="inlineStr"/>
       <c r="L38" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABPCL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABB</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>BHEL</t>
+          <t>INDHOTEL</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -4120,14 +4092,14 @@
       <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABHEL</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AINDHOTEL</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>NMDC</t>
+          <t>BANDHANBNK</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -4150,14 +4122,14 @@
       <c r="K40" t="inlineStr"/>
       <c r="L40" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANMDC</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABANDHANBNK</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>IDFCFIRSTB</t>
+          <t>NTPC</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -4170,7 +4142,7 @@
       <c r="E41" t="inlineStr"/>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Bearish ND</t>
+          <t>Bullish ND</t>
         </is>
       </c>
       <c r="G41" t="inlineStr"/>
@@ -4180,14 +4152,14 @@
       <c r="K41" t="inlineStr"/>
       <c r="L41" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AIDFCFIRSTB</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANTPC</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>NIFTY</t>
+          <t>PREMIERENE</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -4210,14 +4182,14 @@
       <c r="K42" t="inlineStr"/>
       <c r="L42" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANIFTY</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APREMIERENE</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>HEROMOTOCO</t>
+          <t>ADANIPORTS</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -4240,14 +4212,14 @@
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHEROMOTOCO</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIPORTS</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>APOLLOHOSP</t>
+          <t>LICHSGFIN</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -4260,7 +4232,7 @@
       <c r="E44" t="inlineStr"/>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Bearish ND</t>
+          <t>Bullish ND</t>
         </is>
       </c>
       <c r="G44" t="inlineStr"/>
@@ -4270,14 +4242,14 @@
       <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr">
         <is>
-          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAPOLLOHOSP</t>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ALICHSGFIN</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>HINDPETRO</t>
+          <t>BHEL</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -4300,6 +4272,2498 @@
       <c r="K45" t="inlineStr"/>
       <c r="L45" t="inlineStr">
         <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABHEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr"/>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr"/>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
+      <c r="J46" t="inlineStr"/>
+      <c r="K46" t="inlineStr"/>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AIDFCFIRSTB</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr"/>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Bullish ND</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr"/>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr"/>
+      <c r="J47" t="inlineStr"/>
+      <c r="K47" t="inlineStr"/>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHEROMOTOCO</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L33"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Signal</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Trend</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Setup</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Divergence</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>RSI</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Zone</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Confluence</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Bias</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Probability</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>TV_Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>NAUKRI</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Bullish ND</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANAUKRI</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>GMRAIRPORT</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AGMRAIRPORT</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>FORTIS</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AFORTIS</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACHOLAFIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>JSWSTEEL</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AJSWSTEEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PERSISTENT</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Bullish ND</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APERSISTENT</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>PAYTM</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APAYTM</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>UPL</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Bullish ND</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AUPL</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>FEDERALBNK</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AFEDERALBNK</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>WIPRO</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Bullish ND</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AWIPRO</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>PIIND</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Bullish ND</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APIIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>LUPIN</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ALUPIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>AUBANK</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAUBANK</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>KAYNES</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Bullish ND</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AKAYNES</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>KPITTECH</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Bullish ND</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AKPITTECH</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TATAELXSI</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Bullish ND</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATATAELXSI</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>KALYANKJIL</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Bullish ND</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AKALYANKJIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>PGEL</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Bullish ND</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APGEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>CNXMIDCAP</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACNXMIDCAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>ITC</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Bullish ND</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AITC</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>PIDILITIND</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Bullish ND</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APIDILITIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATITAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>TATACONSUM</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATATACONSUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>SUPREMEIND</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Bullish ND</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASUPREMEIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>IRFC</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Bullish ND</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AIRFC</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>TATASTEEL</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATATASTEEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>INDIANB</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AINDIANB</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>ABCAPITAL</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AABCAPITAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>BAJFINANCE</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABAJFINANCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Bullish ND</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABHEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>OIL</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AOIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>LTF</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ALTF</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:L45"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Symbol</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>Signal</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>Trend</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>State</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Setup</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>Divergence</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>RSI</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>Zone</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>Confluence</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>Bias</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>Probability</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>TV_Link</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>SAIL</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr"/>
+      <c r="D2" t="inlineStr"/>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr"/>
+      <c r="I2" t="inlineStr"/>
+      <c r="J2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASAIL</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>ETERNAL</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AETERNAL</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>ANGELONE</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr"/>
+      <c r="I4" t="inlineStr"/>
+      <c r="J4" t="inlineStr"/>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AANGELONE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>GMRAIRPORT</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr"/>
+      <c r="D5" t="inlineStr"/>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr"/>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AGMRAIRPORT</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>CHOLAFIN</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr"/>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr"/>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACHOLAFIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>NESTLEIND</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr"/>
+      <c r="I7" t="inlineStr"/>
+      <c r="J7" t="inlineStr"/>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANESTLEIND</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>LT</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr"/>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="J8" t="inlineStr"/>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ALT</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AUROPHARMA</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr"/>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr"/>
+      <c r="J9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAUROPHARMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>M&amp;M</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr"/>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr"/>
+      <c r="J10" t="inlineStr"/>
+      <c r="K10" t="inlineStr"/>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AM&amp;M</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>BOSCHLTD</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr"/>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr"/>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr"/>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABOSCHLTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>APLAPOLLO</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr"/>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr"/>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr"/>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAPLAPOLLO</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>RELIANCE</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr"/>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr"/>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr"/>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ARELIANCE</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>KEI</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr"/>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr"/>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr"/>
+      <c r="J14" t="inlineStr"/>
+      <c r="K14" t="inlineStr"/>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AKEI</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>ULTRACEMCO</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr"/>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr"/>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr"/>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AULTRACEMCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>MOTILALOFS</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr"/>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr"/>
+      <c r="J16" t="inlineStr"/>
+      <c r="K16" t="inlineStr"/>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMOTILALOFS</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>UNOMINDA</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr"/>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr"/>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr"/>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr"/>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AUNOMINDA</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>POLYCAB</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr"/>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr"/>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr"/>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr"/>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APOLYCAB</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>CGPOWER</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr"/>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr"/>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr"/>
+      <c r="J19" t="inlineStr"/>
+      <c r="K19" t="inlineStr"/>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACGPOWER</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>SUNPHARMA</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr"/>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr"/>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr"/>
+      <c r="J20" t="inlineStr"/>
+      <c r="K20" t="inlineStr"/>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ASUNPHARMA</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>MOTHERSON</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr"/>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr"/>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr"/>
+      <c r="J21" t="inlineStr"/>
+      <c r="K21" t="inlineStr"/>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AMOTHERSON</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>JINDALSTEL</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr"/>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr"/>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr"/>
+      <c r="J22" t="inlineStr"/>
+      <c r="K22" t="inlineStr"/>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AJINDALSTEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>GRASIM</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr"/>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr"/>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr"/>
+      <c r="J23" t="inlineStr"/>
+      <c r="K23" t="inlineStr"/>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AGRASIM</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>BANKINDIA</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr"/>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr"/>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABANKINDIA</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>LUPIN</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr"/>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr"/>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr"/>
+      <c r="J25" t="inlineStr"/>
+      <c r="K25" t="inlineStr"/>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ALUPIN</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>CNXMIDCAP</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr"/>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr"/>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr"/>
+      <c r="J26" t="inlineStr"/>
+      <c r="K26" t="inlineStr"/>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACNXMIDCAP</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>PHOENIXLTD</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr"/>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr"/>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
+      <c r="J27" t="inlineStr"/>
+      <c r="K27" t="inlineStr"/>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3APHOENIXLTD</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>UNIONBANK</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr"/>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr"/>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr"/>
+      <c r="J28" t="inlineStr"/>
+      <c r="K28" t="inlineStr"/>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AUNIONBANK</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>TITAN</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr"/>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr"/>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr"/>
+      <c r="J29" t="inlineStr"/>
+      <c r="K29" t="inlineStr"/>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATITAN</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>INDUSTOWER</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr"/>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr"/>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr"/>
+      <c r="J30" t="inlineStr"/>
+      <c r="K30" t="inlineStr"/>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AINDUSTOWER</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>TATACONSUM</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr"/>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr"/>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr"/>
+      <c r="J31" t="inlineStr"/>
+      <c r="K31" t="inlineStr"/>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATATACONSUM</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>DALBHARAT</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr"/>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr"/>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr"/>
+      <c r="J32" t="inlineStr"/>
+      <c r="K32" t="inlineStr"/>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ADALBHARAT</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>TECHM</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr"/>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr"/>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr"/>
+      <c r="J33" t="inlineStr"/>
+      <c r="K33" t="inlineStr"/>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ATECHM</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>CANBK</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr"/>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr"/>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr"/>
+      <c r="J34" t="inlineStr"/>
+      <c r="K34" t="inlineStr"/>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ACANBK</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>ADANIPORTS</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr"/>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr"/>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr"/>
+      <c r="J35" t="inlineStr"/>
+      <c r="K35" t="inlineStr"/>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AADANIPORTS</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>BANKBARODA</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr"/>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr"/>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr"/>
+      <c r="J36" t="inlineStr"/>
+      <c r="K36" t="inlineStr"/>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABANKBARODA</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>AXISBANK</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr"/>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr"/>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr"/>
+      <c r="J37" t="inlineStr"/>
+      <c r="K37" t="inlineStr"/>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAXISBANK</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>BPCL</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr"/>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr"/>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr"/>
+      <c r="J38" t="inlineStr"/>
+      <c r="K38" t="inlineStr"/>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABPCL</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>BHEL</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr"/>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr"/>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr"/>
+      <c r="J39" t="inlineStr"/>
+      <c r="K39" t="inlineStr"/>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ABHEL</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>NMDC</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr"/>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr"/>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr"/>
+      <c r="J40" t="inlineStr"/>
+      <c r="K40" t="inlineStr"/>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANMDC</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>IDFCFIRSTB</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr"/>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr"/>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr"/>
+      <c r="J41" t="inlineStr"/>
+      <c r="K41" t="inlineStr"/>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AIDFCFIRSTB</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>NIFTY</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr"/>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr"/>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr"/>
+      <c r="J42" t="inlineStr"/>
+      <c r="K42" t="inlineStr"/>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3ANIFTY</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>HEROMOTOCO</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr"/>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr"/>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
+      <c r="J43" t="inlineStr"/>
+      <c r="K43" t="inlineStr"/>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHEROMOTOCO</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>APOLLOHOSP</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr"/>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr"/>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr"/>
+      <c r="J44" t="inlineStr"/>
+      <c r="K44" t="inlineStr"/>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AAPOLLOHOSP</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>HINDPETRO</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Divergence Alert</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr"/>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Bearish ND</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr"/>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr"/>
+      <c r="J45" t="inlineStr"/>
+      <c r="K45" t="inlineStr"/>
+      <c r="L45" t="inlineStr">
+        <is>
           <t>https://in.tradingview.com/chart/LqUZraZ9/?symbol=NSE%3AHINDPETRO</t>
         </is>
       </c>
